--- a/synthetic/documents/xlsx/order_117_NMC-01116.xlsx
+++ b/synthetic/documents/xlsx/order_117_NMC-01116.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -471,7 +471,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Northern Manufacturing Corp. (SYNTHETIC)</t>
+          <t>Atlas Group (SYNTHETIC)</t>
         </is>
       </c>
     </row>
@@ -495,7 +495,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -507,7 +507,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Grand Rapids Factory</t>
+          <t>Atlas Shipping Location 3</t>
         </is>
       </c>
     </row>
@@ -554,16 +554,16 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>NM-JS-9138</t>
+          <t>ATLAS-LUB-7716</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Can Liner 40x48 0.5mil Black 100/CS</t>
+          <t>Penetrating Oil Spray (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
@@ -571,10 +571,10 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>52.01</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>624.12</v>
+        <v>676.5</v>
       </c>
     </row>
     <row r="10">
@@ -583,27 +583,27 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>FST-HCS-51618-1-G8-B50</t>
+          <t>ATLAS-JAN-4268</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Hex Cap Screw 5/16-18 x 1" Grade 8 Yellow Zinc</t>
+          <t>Toilet Tissue 2P Standard (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>16.55</v>
+        <v>69.44</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>16.55</v>
+        <v>694.4</v>
       </c>
     </row>
     <row r="11">
@@ -612,27 +612,27 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>PPE-GGL-OTG</t>
+          <t>FST-FWS-M10</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Safety Goggles over-the-glasses clear</t>
+          <t>Flat Washer M10 Zinc (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>7.25</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>29</v>
+        <v>97.68000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -641,27 +641,27 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>NM-HW-6263</t>
+          <t>ATLAS-JAN-7596</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Hex Cap Screw 5/16-18 x 1-1/2" Stainless 18-8</t>
+          <t>Can Liner 40x46 0.7mil Black Roll (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>35.14</v>
+        <v>20.77</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>70.28</v>
+        <v>20.77</v>
       </c>
     </row>
     <row r="13">
@@ -670,85 +670,27 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>FST-FHCS-1420-1-SS-B25</t>
+          <t>PPE-GLV-LAT-5-XXL-WHI</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Flat Head Cap Screw 1/4-20 x 1" Stainless 18-8</t>
+          <t>Latex Gloves XXL PF (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>32.96</v>
+        <v>72.2</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>329.6</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>NM-MIS-5753</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Pry Bar 12 inch</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>11.02</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>264.48</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>NM-PPE-9306</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Latex Exam Gloves 8 mil powder-free Natural size L</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>CS</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>118.4</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>2841.6</v>
+        <v>216.6</v>
       </c>
     </row>
   </sheetData>

--- a/synthetic/documents/xlsx/order_117_NMC-01116.xlsx
+++ b/synthetic/documents/xlsx/order_117_NMC-01116.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Purchase Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purchase Order" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -511,84 +511,67 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Delivery Date:</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Item Code</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>UoM</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>Unit Price</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>ATLAS-LUB-7716</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Penetrating Oil Spray (SYNTHETIC)</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>CS</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>67.65000000000001</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>676.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>ATLAS-JAN-4268</t>
+          <t>ATLAS-LUB-7716</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Toilet Tissue 2P Standard (SYNTHETIC)</t>
+          <t>Penetrating Oil Spray (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
@@ -600,96 +583,125 @@
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>69.44</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>694.4</v>
+        <v>676.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>FST-FWS-M10</t>
+          <t>ATLAS-JAN-4268</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Flat Washer M10 Zinc (SYNTHETIC)</t>
+          <t>Toilet Tissue 2P Standard (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>8.140000000000001</v>
+        <v>69.44</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>97.68000000000001</v>
+        <v>694.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>ATLAS-JAN-7596</t>
+          <t>FST-FWS-M10</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Can Liner 40x46 0.7mil Black Roll (SYNTHETIC)</t>
+          <t>Flat Washer M10 Zinc (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>20.77</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>20.77</v>
+        <v>97.68000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>ATLAS-JAN-7596</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Can Liner 40x46 0.7mil Black Roll (SYNTHETIC)</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>20.77</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>20.77</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>PPE-GLV-LAT-5-XXL-WHI</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Latex Gloves XXL PF (SYNTHETIC)</t>
         </is>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D14" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="F14" s="4" t="n">
         <v>72.2</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>216.6</v>
       </c>
     </row>
